--- a/myapp/docs/app_specifications.xlsx
+++ b/myapp/docs/app_specifications.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ts-ken.a.ichinose/git/training/trainingapp/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ts-ken.a.ichinose/git/training/myapp/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A837F5DF-4255-CA44-8C66-D417B7BC03AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3BD92B-A886-C943-9997-59619BC2A147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="500" windowWidth="28300" windowHeight="15820" xr2:uid="{845D9701-9E1B-8F44-AC54-33FB97E5CA0E}"/>
+    <workbookView xWindow="500" yWindow="500" windowWidth="28300" windowHeight="15820" activeTab="1" xr2:uid="{845D9701-9E1B-8F44-AC54-33FB97E5CA0E}"/>
   </bookViews>
   <sheets>
     <sheet name="画面イメージ" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="79">
   <si>
     <t>タスク名</t>
     <phoneticPr fontId="1"/>
@@ -398,10 +398,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>t_login</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>CURRENT_TIMESTAMP</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -446,6 +442,22 @@
   </si>
   <si>
     <t>　　　　　　　　　　　　　　　▼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>t_users</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>varchar(100)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>create_dt</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>update_dt</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1707,11 +1719,11 @@
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5"/>
       <c r="K10" s="3"/>
@@ -1773,7 +1785,7 @@
         <v>6</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N12" s="26"/>
       <c r="O12" s="27"/>
@@ -1908,7 +1920,7 @@
         <v>6</v>
       </c>
       <c r="W18" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X18" s="26"/>
       <c r="Y18" s="27"/>
@@ -1986,7 +1998,7 @@
       </c>
       <c r="X22" s="4"/>
       <c r="Y22" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z22" s="5"/>
     </row>
@@ -2295,7 +2307,7 @@
       </c>
       <c r="X43" s="4"/>
       <c r="Y43" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z43" s="5"/>
     </row>
@@ -2415,7 +2427,7 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="2:7">
@@ -2509,7 +2521,7 @@
         <v>60</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>62</v>
@@ -2518,7 +2530,7 @@
         <v>51</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8" s="15"/>
     </row>
@@ -2527,7 +2539,7 @@
         <v>61</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>62</v>
@@ -2591,7 +2603,7 @@
         <v>54</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>51</v>
@@ -2607,7 +2619,7 @@
         <v>55</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>51</v>
@@ -2617,10 +2629,10 @@
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>50</v>
@@ -2632,7 +2644,7 @@
         <v>42</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -2643,7 +2655,7 @@
         <v>56</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>51</v>
@@ -2709,13 +2721,13 @@
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>68</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>69</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>51</v>
@@ -2724,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -2748,7 +2760,7 @@
         <v>60</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>62</v>
@@ -2757,7 +2769,7 @@
         <v>51</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G24" s="15"/>
     </row>
@@ -2766,7 +2778,7 @@
         <v>61</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>62</v>
